--- a/projects/mister-campaign-box/TransitTimes.xlsx
+++ b/projects/mister-campaign-box/TransitTimes.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23A8511-44AA-46AB-B8A7-808B3E4AC35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F48FDE0-A7A4-4375-9638-4B698B674B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19125" yWindow="795" windowWidth="16935" windowHeight="9930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transit" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="4">
   <si>
     <t>Store Number</t>
   </si>
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -455,10 +455,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>651</v>
+        <v>205</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -466,10 +466,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>388</v>
+        <v>206</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -477,10 +477,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>389</v>
+        <v>208</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -488,10 +488,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>391</v>
+        <v>209</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -499,10 +499,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
@@ -510,10 +510,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>393</v>
+        <v>228</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -521,10 +521,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>394</v>
+        <v>229</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
@@ -532,10 +532,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>395</v>
+        <v>230</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
@@ -543,10 +543,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>396</v>
+        <v>231</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>397</v>
+        <v>234</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -565,10 +565,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>1388</v>
+        <v>276</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
@@ -576,10 +576,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1391</v>
+        <v>277</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -587,10 +587,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1393</v>
+        <v>278</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>3</v>
@@ -598,10 +598,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>831</v>
+        <v>1207</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -609,10 +609,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>833</v>
+        <v>1211</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>836</v>
+        <v>1212</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>838</v>
+        <v>1213</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
@@ -642,10 +642,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>839</v>
+        <v>1214</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
@@ -653,10 +653,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>840</v>
+        <v>1223</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -664,10 +664,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>841</v>
+        <v>1233</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -675,10 +675,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>842</v>
+        <v>1234</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -686,10 +686,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>843</v>
+        <v>1235</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
@@ -697,10 +697,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>845</v>
+        <v>1237</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
@@ -708,10 +708,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>511</v>
+        <v>1238</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
         <v>3</v>
@@ -719,10 +719,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>512</v>
+        <v>1239</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
@@ -730,10 +730,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>522</v>
+        <v>1241</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
@@ -741,10 +741,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>524</v>
+        <v>1244</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -752,10 +752,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>525</v>
+        <v>1253</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
@@ -763,10 +763,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>526</v>
+        <v>1002</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
@@ -774,10 +774,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>528</v>
+        <v>1004</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
         <v>3</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>531</v>
+        <v>1005</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>535</v>
+        <v>1006</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
@@ -807,10 +807,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1511</v>
+        <v>1007</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
@@ -818,10 +818,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>575</v>
+        <v>1008</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -829,10 +829,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>577</v>
+        <v>1009</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
@@ -840,10 +840,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>578</v>
+        <v>1010</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
         <v>3</v>
@@ -851,10 +851,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>579</v>
+        <v>1011</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
         <v>3</v>
@@ -862,10 +862,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>580</v>
+        <v>1051</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
@@ -873,10 +873,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>581</v>
+        <v>1055</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>582</v>
+        <v>1057</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>583</v>
+        <v>1001</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -906,10 +906,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1577</v>
+        <v>1003</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>801</v>
+        <v>921</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
@@ -928,10 +928,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>802</v>
+        <v>923</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
         <v>3</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>601</v>
+        <v>925</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
         <v>3</v>
@@ -950,10 +950,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>605</v>
+        <v>928</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
         <v>3</v>
@@ -961,10 +961,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>606</v>
+        <v>930</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
         <v>3</v>
@@ -972,10 +972,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>608</v>
+        <v>933</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
@@ -983,10 +983,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>612</v>
+        <v>942</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
         <v>3</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>401</v>
+        <v>943</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
         <v>3</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>430</v>
+        <v>1014</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
         <v>3</v>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>451</v>
+        <v>1039</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>452</v>
+        <v>1052</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
         <v>3</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>613</v>
+        <v>1053</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
@@ -1049,10 +1049,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>602</v>
+        <v>1054</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
         <v>3</v>
@@ -1060,10 +1060,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>614</v>
+        <v>1056</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>1612</v>
+        <v>1072</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
         <v>3</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>1601</v>
+        <v>571</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>1602</v>
+        <v>572</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C61" t="s">
         <v>3</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>1611</v>
+        <v>573</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>1616</v>
+        <v>574</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C63" t="s">
         <v>3</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>1479</v>
+        <v>1578</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>386</v>
+        <v>1579</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="s">
         <v>3</v>
@@ -1159,10 +1159,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>387</v>
+        <v>1580</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="s">
         <v>3</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>1390</v>
+        <v>911</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="s">
         <v>3</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>1396</v>
+        <v>912</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="s">
         <v>3</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>351</v>
+        <v>914</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="s">
         <v>3</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>352</v>
+        <v>916</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="s">
         <v>3</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>353</v>
+        <v>918</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="s">
         <v>3</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>354</v>
+        <v>919</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="s">
         <v>3</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>361</v>
+        <v>920</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="s">
         <v>3</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>362</v>
+        <v>922</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
         <v>3</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>363</v>
+        <v>924</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" t="s">
         <v>3</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>364</v>
+        <v>926</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="s">
         <v>3</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>365</v>
+        <v>927</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>366</v>
+        <v>929</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>3</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>355</v>
+        <v>931</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="s">
         <v>3</v>
@@ -1313,133 +1313,12 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>356</v>
+        <v>940</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>357</v>
-      </c>
-      <c r="B81">
-        <v>2</v>
-      </c>
-      <c r="C81" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>367</v>
-      </c>
-      <c r="B82">
-        <v>2</v>
-      </c>
-      <c r="C82" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>368</v>
-      </c>
-      <c r="B83">
-        <v>2</v>
-      </c>
-      <c r="C83" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>369</v>
-      </c>
-      <c r="B84">
-        <v>2</v>
-      </c>
-      <c r="C84" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>1352</v>
-      </c>
-      <c r="B85">
-        <v>2</v>
-      </c>
-      <c r="C85" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>1353</v>
-      </c>
-      <c r="B86">
-        <v>2</v>
-      </c>
-      <c r="C86" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>375</v>
-      </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>1355</v>
-      </c>
-      <c r="B88">
-        <v>2</v>
-      </c>
-      <c r="C88" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>1358</v>
-      </c>
-      <c r="B89">
-        <v>2</v>
-      </c>
-      <c r="C89" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>1354</v>
-      </c>
-      <c r="B90">
-        <v>2</v>
-      </c>
-      <c r="C90" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>1356</v>
-      </c>
-      <c r="B91">
-        <v>2</v>
-      </c>
-      <c r="C91" t="s">
         <v>3</v>
       </c>
     </row>
